--- a/src/nodes/HPC/compressor_stage_6_blade_stator_coordinates_foil.xlsx
+++ b/src/nodes/HPC/compressor_stage_6_blade_stator_coordinates_foil.xlsx
@@ -1023,7 +1023,7 @@
         <v>0.00058099782035625773</v>
       </c>
       <c r="B2">
-        <v>0.0004667941818967761</v>
+        <v>0.00050978802060313915</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.0011619956407125155</v>
       </c>
       <c r="B3">
-        <v>0.0007848328530931615</v>
+        <v>0.00084409463076949966</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.0017429934610687734</v>
       </c>
       <c r="B4">
-        <v>0.0010695555159621389</v>
+        <v>0.0011413668465581723</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.0023239912814250309</v>
       </c>
       <c r="B5">
-        <v>0.0013277172329580192</v>
+        <v>0.0014096379256282514</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.0029049891017812884</v>
       </c>
       <c r="B6">
-        <v>0.0015622531382159396</v>
+        <v>0.001652363739744698</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.0034859869221375468</v>
       </c>
       <c r="B7">
-        <v>0.0017749414402881689</v>
+        <v>0.00187161947759545</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.0040669847424938043</v>
       </c>
       <c r="B8">
-        <v>0.0019669296715600373</v>
+        <v>0.00206872704188384</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.0046479825628500619</v>
       </c>
       <c r="B9">
-        <v>0.002139821831985</v>
+        <v>0.0022455634352898392</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.0052289803832063194</v>
       </c>
       <c r="B10">
-        <v>0.002295314340015319</v>
+        <v>0.0024041198983543038</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.0058099782035625769</v>
       </c>
       <c r="B11">
-        <v>0.0024350168205303571</v>
+        <v>0.0025462895230849874</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.0063909760239188353</v>
       </c>
       <c r="B12">
-        <v>0.0025598630874878823</v>
+        <v>0.002673157249122001</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.0069719738442750936</v>
       </c>
       <c r="B13">
-        <v>0.0026681705047321793</v>
+        <v>0.0027826735551679908</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.00755297166463135</v>
       </c>
       <c r="B14">
-        <v>0.00275898013121896</v>
+        <v>0.0028736599428105165</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.0081339694849876087</v>
       </c>
       <c r="B15">
-        <v>0.0028368442564631236</v>
+        <v>0.0029515564661142623</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.0087149673053438653</v>
       </c>
       <c r="B16">
-        <v>0.0029059371072502477</v>
+        <v>0.0030213516053281203</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.0092959651257001237</v>
       </c>
       <c r="B17">
-        <v>0.0029634094288894441</v>
+        <v>0.003079608992960696</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.0098769629460563821</v>
       </c>
       <c r="B18">
-        <v>0.0030055445688691122</v>
+        <v>0.0031218539124475159</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.010457960766412639</v>
       </c>
       <c r="B19">
-        <v>0.0030321797648712725</v>
+        <v>0.0031478830986720794</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.011038958586768897</v>
       </c>
       <c r="B20">
-        <v>0.0030440407271263526</v>
+        <v>0.0031585611493798785</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.011619956407125154</v>
       </c>
       <c r="B21">
-        <v>0.0030418531658647787</v>
+        <v>0.0031547526623164068</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.012200954227481412</v>
       </c>
       <c r="B22">
-        <v>0.0030262090129088092</v>
+        <v>0.0031371637426271391</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.012781952047837671</v>
       </c>
       <c r="B23">
-        <v>0.0029971650864480275</v>
+        <v>0.0031058665250574846</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.013362949868193929</v>
       </c>
       <c r="B24">
-        <v>0.0029546444262638482</v>
+        <v>0.0030607746517528358</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.013943947688550187</v>
       </c>
       <c r="B25">
-        <v>0.0028985700721376861</v>
+        <v>0.0030018017648585859</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.014524945508906442</v>
       </c>
       <c r="B26">
-        <v>0.0028288344652820994</v>
+        <v>0.0029288268482282136</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.0151059433292627</v>
       </c>
       <c r="B27">
-        <v>0.0027452076526342179</v>
+        <v>0.0028415902525475456</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.015686941149618959</v>
       </c>
       <c r="B28">
-        <v>0.0026474290825623157</v>
+        <v>0.0027397976702104952</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.016267938969975217</v>
       </c>
       <c r="B29">
-        <v>0.0025352382034346667</v>
+        <v>0.0026231547936109755</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.016848936790331476</v>
       </c>
       <c r="B30">
-        <v>0.0024084548075153536</v>
+        <v>0.002491466098457244</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.017429934610687731</v>
       </c>
       <c r="B31">
-        <v>0.0022672200626516971</v>
+        <v>0.002344931193714934</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.018010932431043989</v>
       </c>
       <c r="B32">
-        <v>0.0021117554805868267</v>
+        <v>0.002183848471664022</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.018591930251400247</v>
       </c>
       <c r="B33">
-        <v>0.0019422825730638724</v>
+        <v>0.0020085163245844857</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.019172928071756506</v>
       </c>
       <c r="B34">
-        <v>0.0017588583439460228</v>
+        <v>0.0018190388825254278</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.019753925892112764</v>
       </c>
       <c r="B35">
-        <v>0.0015608817655766993</v>
+        <v>0.0016147432266124546</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.020334923712469019</v>
       </c>
       <c r="B36">
-        <v>0.0013475873024193831</v>
+        <v>0.0013947621757402994</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.020915921532825277</v>
       </c>
       <c r="B37">
-        <v>0.0011182094189375526</v>
+        <v>0.0011582285488036916</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.021496919353181536</v>
       </c>
       <c r="B38">
-        <v>0.00087159893942227154</v>
+        <v>0.00090381852941131191</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.022077917173537794</v>
       </c>
       <c r="B39">
-        <v>0.00060507212747493416</v>
+        <v>0.00062838176002762711</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.022658914993894053</v>
       </c>
       <c r="B40">
-        <v>0.00031556160652451747</v>
+        <v>0.00032831124783105138</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.022658914993894053</v>
       </c>
       <c r="B43">
-        <v>0.00018806519345917894</v>
+        <v>0.00017531555215264503</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.022077917173537794</v>
       </c>
       <c r="B44">
-        <v>0.00037197580194800407</v>
+        <v>0.000348666169395311</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.021496919353181536</v>
       </c>
       <c r="B45">
-        <v>0.00054940303953186754</v>
+        <v>0.00051718344954282706</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.020915921532825277</v>
       </c>
       <c r="B46">
-        <v>0.00071801812027616236</v>
+        <v>0.00067799899041002328</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.020334923712469019</v>
       </c>
       <c r="B47">
-        <v>0.00087583856921022234</v>
+        <v>0.00082866369588930635</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.019753925892112764</v>
       </c>
       <c r="B48">
-        <v>0.0010222671552191451</v>
+        <v>0.00096840569418338968</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.019172928071756506</v>
       </c>
       <c r="B49">
-        <v>0.001157052958151971</v>
+        <v>0.0010968724195725658</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.018591930251400247</v>
       </c>
       <c r="B50">
-        <v>0.0012799450578577388</v>
+        <v>0.0012137113063371253</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.018010932431043989</v>
       </c>
       <c r="B51">
-        <v>0.0013908255698148711</v>
+        <v>0.0013187325787376754</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.017429934610687731</v>
       </c>
       <c r="B52">
-        <v>0.0014901087520193266</v>
+        <v>0.0014123976209560896</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.016848936790331476</v>
       </c>
       <c r="B53">
-        <v>0.0015783418980964479</v>
+        <v>0.0014953306071545573</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.016267938969975217</v>
       </c>
       <c r="B54">
-        <v>0.0016560723016715777</v>
+        <v>0.0015681557114952689</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.015686941149618959</v>
       </c>
       <c r="B55">
-        <v>0.001723743206080522</v>
+        <v>0.0016313746184323428</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.0151059433292627</v>
       </c>
       <c r="B56">
-        <v>0.0017813816535009396</v>
+        <v>0.001684999053587612</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.014524945508906442</v>
       </c>
       <c r="B57">
-        <v>0.0018289106358209538</v>
+        <v>0.0017289182528748396</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.013943947688550187</v>
       </c>
       <c r="B58">
-        <v>0.0018662531449286871</v>
+        <v>0.0017630214522077875</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.013362949868193929</v>
       </c>
       <c r="B59">
-        <v>0.001893342171373969</v>
+        <v>0.0017872119458849814</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.012781952047837671</v>
       </c>
       <c r="B60">
-        <v>0.0019101507003534558</v>
+        <v>0.001801449261743999</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.012200954227481412</v>
       </c>
       <c r="B61">
-        <v>0.0019166617157255113</v>
+        <v>0.001805706986007182</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.011619956407125154</v>
       </c>
       <c r="B62">
-        <v>0.0019128582013484986</v>
+        <v>0.0017999587048968709</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.011038958586768897</v>
       </c>
       <c r="B63">
-        <v>0.0018988365045910919</v>
+        <v>0.001784316082337566</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.010457960766412639</v>
       </c>
       <c r="B64">
-        <v>0.0018751464268632091</v>
+        <v>0.0017594430930624027</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.0098769629460563821</v>
       </c>
       <c r="B65">
-        <v>0.0018424511330850787</v>
+        <v>0.0017261417895066749</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.0092959651257001237</v>
       </c>
       <c r="B66">
-        <v>0.0018014137881769291</v>
+        <v>0.0016852142241056776</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.0087149673053438653</v>
       </c>
       <c r="B67">
-        <v>0.0017517921264715193</v>
+        <v>0.0016363776283936464</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.0081339694849876087</v>
       </c>
       <c r="B68">
-        <v>0.0016897221599517275</v>
+        <v>0.0015750099503005881</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.00755297166463135</v>
       </c>
       <c r="B69">
-        <v>0.0016121820153033922</v>
+        <v>0.0014975022037118355</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.0069719738442750936</v>
       </c>
       <c r="B70">
-        <v>0.0015231400003740665</v>
+        <v>0.0014086369499382552</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.0063909760239188353</v>
       </c>
       <c r="B71">
-        <v>0.0014269214711466929</v>
+        <v>0.0013136273095125741</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.0058099782035625769</v>
       </c>
       <c r="B72">
-        <v>0.0013222897949840523</v>
+        <v>0.001211017092429422</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.0052289803832063194</v>
       </c>
       <c r="B73">
-        <v>0.0012072587566254699</v>
+        <v>0.001098453198286485</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.0046479825628500619</v>
       </c>
       <c r="B74">
-        <v>0.0010824057989366109</v>
+        <v>0.000976664195631772</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.0040669847424938043</v>
       </c>
       <c r="B75">
-        <v>0.00094895596832201222</v>
+        <v>0.00084715859799820974</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.0034859869221375468</v>
       </c>
       <c r="B76">
-        <v>0.00080816106721535606</v>
+        <v>0.00071148302990807477</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.0029049891017812884</v>
       </c>
       <c r="B77">
-        <v>0.00066114712292835484</v>
+        <v>0.00057103652139959638</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.0023239912814250309</v>
       </c>
       <c r="B78">
-        <v>0.00050851030625569582</v>
+        <v>0.00042658961358546358</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.0017429934610687734</v>
       </c>
       <c r="B79">
-        <v>0.00035144221000180434</v>
+        <v>0.00027963087940577092</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.0011619956407125155</v>
       </c>
       <c r="B80">
-        <v>0.00019221507632977876</v>
+        <v>0.00013295329865344049</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.00058099782035625773</v>
       </c>
       <c r="B81">
-        <v>3.6855794833145385E-05</v>
+        <v>-6.1380438732176643E-06</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.00063074692357243268</v>
       </c>
       <c r="B2">
-        <v>0.00059862505777543828</v>
+        <v>0.00069197560246415815</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.0012614938471448654</v>
       </c>
       <c r="B3">
-        <v>0.000977843495546673</v>
+        <v>0.0011065158679554495</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.0018922407707172983</v>
       </c>
       <c r="B4">
-        <v>0.0013129270865711595</v>
+        <v>0.0014688477260782649</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.0025229876942897307</v>
       </c>
       <c r="B5">
-        <v>0.0016139778675095921</v>
+        <v>0.0017918484999570178</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.0031537346178621634</v>
       </c>
       <c r="B6">
-        <v>0.0018853069705983636</v>
+        <v>0.00208095997549492</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.0037844815414345965</v>
       </c>
       <c r="B7">
-        <v>0.0021294845370131246</v>
+        <v>0.0023393971131780303</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.0044152284650070288</v>
       </c>
       <c r="B8">
-        <v>0.0023481301825415456</v>
+        <v>0.0025691581310461737</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.0050459753885794614</v>
       </c>
       <c r="B9">
-        <v>0.0025435739825605788</v>
+        <v>0.0027731658627409444</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.0056767223121518941</v>
       </c>
       <c r="B10">
-        <v>0.0027182940492203752</v>
+        <v>0.0029545385540545367</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.0063074692357243268</v>
       </c>
       <c r="B11">
-        <v>0.0028746501821746012</v>
+        <v>0.0031162514837797862</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.00693821615929676</v>
       </c>
       <c r="B12">
-        <v>0.003013981415163321</v>
+        <v>0.0032599718179005307</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.007568963082869193</v>
       </c>
       <c r="B13">
-        <v>0.003133662030768676</v>
+        <v>0.0033822772381639859</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.0081997100064416257</v>
       </c>
       <c r="B14">
-        <v>0.0032321720840107174</v>
+        <v>0.003481171084774221</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.0088304569300140575</v>
       </c>
       <c r="B15">
-        <v>0.0033163794708190629</v>
+        <v>0.0035654488159993459</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.009461203853586491</v>
       </c>
       <c r="B16">
-        <v>0.0033925822142122737</v>
+        <v>0.0036431764059551503</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.010091950777158923</v>
       </c>
       <c r="B17">
-        <v>0.0034564110046551209</v>
+        <v>0.0037087097740840934</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.010722697700731356</v>
       </c>
       <c r="B18">
-        <v>0.0035021838805138132</v>
+        <v>0.0037547210091378848</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.011353444624303788</v>
       </c>
       <c r="B19">
-        <v>0.0035296356043140907</v>
+        <v>0.0037808569317785649</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.011984191547876222</v>
       </c>
       <c r="B20">
-        <v>0.003539855119621578</v>
+        <v>0.0037885080456457583</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.012614938471448654</v>
       </c>
       <c r="B21">
-        <v>0.0035339313700018986</v>
+        <v>0.0037790648543790883</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.013245685395021087</v>
       </c>
       <c r="B22">
-        <v>0.003512754557016805</v>
+        <v>0.003753665458826157</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.013876432318593521</v>
       </c>
       <c r="B23">
-        <v>0.0034764199142125582</v>
+        <v>0.0037124383486664809</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.014507179242165953</v>
       </c>
       <c r="B24">
-        <v>0.0034248239331315477</v>
+        <v>0.0036552596107875517</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.015137926165738386</v>
       </c>
       <c r="B25">
-        <v>0.0033578631053161642</v>
+        <v>0.0035820053320768631</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.015768673089310816</v>
       </c>
       <c r="B26">
-        <v>0.0032753920476002217</v>
+        <v>0.0034925009100233721</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.016399420012883251</v>
       </c>
       <c r="B27">
-        <v>0.0031770978779832415</v>
+        <v>0.0033863689845218758</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.017030166936455683</v>
       </c>
       <c r="B28">
-        <v>0.0030626258397561707</v>
+        <v>0.0032631815060686358</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.017660913860028115</v>
       </c>
       <c r="B29">
-        <v>0.0029316211762099535</v>
+        <v>0.0031225104251599144</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.01829166078360055</v>
       </c>
       <c r="B30">
-        <v>0.0027838565886400307</v>
+        <v>0.002964095186957897</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.018922407707172982</v>
       </c>
       <c r="B31">
-        <v>0.0026196146103598132</v>
+        <v>0.0027883452152884687</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.019553154630745414</v>
       </c>
       <c r="B32">
-        <v>0.0024393052326872021</v>
+        <v>0.0025958374286434386</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.020183901554317846</v>
       </c>
       <c r="B33">
-        <v>0.0022433384469401009</v>
+        <v>0.0023871487455146157</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.020814648477890281</v>
       </c>
       <c r="B34">
-        <v>0.0020318813466402943</v>
+        <v>0.00216254858234392</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.021445395401462713</v>
       </c>
       <c r="B35">
-        <v>0.001804129434125094</v>
+        <v>0.0019210763473737106</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.022076142325035145</v>
       </c>
       <c r="B36">
-        <v>0.0015590353139356941</v>
+        <v>0.0016614639467964559</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.022706889248607576</v>
       </c>
       <c r="B37">
-        <v>0.0012955515906132851</v>
+        <v>0.0013824432868046234</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.023337636172180012</v>
       </c>
       <c r="B38">
-        <v>0.0010120562943737889</v>
+        <v>0.0010820132083322305</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.023968383095752444</v>
       </c>
       <c r="B39">
-        <v>0.00070462915813203678</v>
+        <v>0.00075524029127948871</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.024599130019324875</v>
       </c>
       <c r="B40">
-        <v>0.000368775340477587</v>
+        <v>0.00039645805028815789</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2001,7 +2001,7 @@
         <v>0.025229876942897307</v>
       </c>
       <c r="B41">
-        <v>-8.7533719657699832E-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2009,7 +2009,7 @@
         <v>0.025229876942897307</v>
       </c>
       <c r="B42">
-        <v>-4.3766859828849916E-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.024599130019324875</v>
       </c>
       <c r="B43">
-        <v>0.00017499637180359067</v>
+        <v>0.00014731366199301972</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.023968383095752444</v>
       </c>
       <c r="B44">
-        <v>0.00035035122609987341</v>
+        <v>0.00029974009295242148</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.023337636172180012</v>
       </c>
       <c r="B45">
-        <v>0.00052235789666469853</v>
+        <v>0.00045240098270625707</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.022706889248607576</v>
       </c>
       <c r="B46">
-        <v>0.00068730971727391668</v>
+        <v>0.00060041802108257852</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.022076142325035145</v>
       </c>
       <c r="B47">
-        <v>0.0008420348839103597</v>
+        <v>0.00073960625104959774</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.021445395401462713</v>
       </c>
       <c r="B48">
-        <v>0.00098550104138478076</v>
+        <v>0.00086855412813616466</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.020814648477890281</v>
       </c>
       <c r="B49">
-        <v>0.0011172106967149158</v>
+        <v>0.00098654346101129</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.020183901554317846</v>
       </c>
       <c r="B50">
-        <v>0.0012366663569184982</v>
+        <v>0.0010928560583439834</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.019553154630745414</v>
       </c>
       <c r="B51">
-        <v>0.0013435798609935481</v>
+        <v>0.0011870476650373116</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.018922407707172982</v>
       </c>
       <c r="B52">
-        <v>0.0014385003758592236</v>
+        <v>0.0012697697709305679</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.01829166078360055</v>
       </c>
       <c r="B53">
-        <v>0.0015221864004149681</v>
+        <v>0.0013419478020971023</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.017660913860028115</v>
       </c>
       <c r="B54">
-        <v>0.0015953964335602266</v>
+        <v>0.0014045071846102658</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.017030166936455683</v>
       </c>
       <c r="B55">
-        <v>0.0016587361755689104</v>
+        <v>0.0014581805092564446</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.016399420012883251</v>
       </c>
       <c r="B56">
-        <v>0.001712200132212807</v>
+        <v>0.0015029290256741738</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.015768673089310816</v>
       </c>
       <c r="B57">
-        <v>0.0017556300106381737</v>
+        <v>0.001538521148215024</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.015137926165738386</v>
       </c>
       <c r="B58">
-        <v>0.0017888675179912662</v>
+        <v>0.0015647252912305662</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.014507179242165953</v>
       </c>
       <c r="B59">
-        <v>0.0018117741895395214</v>
+        <v>0.0015813385118835178</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.013876432318593521</v>
       </c>
       <c r="B60">
-        <v>0.0018242908730350977</v>
+        <v>0.001588272438581175</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.013245685395021087</v>
       </c>
       <c r="B61">
-        <v>0.0018263782443513333</v>
+        <v>0.0015854673425419806</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.012614938471448654</v>
       </c>
       <c r="B62">
-        <v>0.0018179969793615668</v>
+        <v>0.0015728634949843767</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.011984191547876222</v>
       </c>
       <c r="B63">
-        <v>0.0017992846374523092</v>
+        <v>0.0015506317114281285</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.011353444624303788</v>
       </c>
       <c r="B64">
-        <v>0.0017710863120627637</v>
+        <v>0.0015198649845982884</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.010722697700731356</v>
       </c>
       <c r="B65">
-        <v>0.0017344239801453051</v>
+        <v>0.0014818868515212328</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.010091950777158923</v>
       </c>
       <c r="B66">
-        <v>0.0016903196186523091</v>
+        <v>0.0014380208492233363</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.009461203853586491</v>
       </c>
       <c r="B67">
-        <v>0.0016384228720121364</v>
+        <v>0.0013878286802692598</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.0088304569300140575</v>
       </c>
       <c r="B68">
-        <v>0.0015728940545570876</v>
+        <v>0.0013238247093768055</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.0081997100064416257</v>
       </c>
       <c r="B69">
-        <v>0.0014891790786661981</v>
+        <v>0.0012401800779026956</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.007568963082869193</v>
       </c>
       <c r="B70">
-        <v>0.0013933555790015056</v>
+        <v>0.0011447403716061957</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.00693821615929676</v>
       </c>
       <c r="B71">
-        <v>0.001292048596002853</v>
+        <v>0.0010460581932656434</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.0063074692357243268</v>
       </c>
       <c r="B72">
-        <v>0.0011834410709383094</v>
+        <v>0.000941839769333125</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.0056767223121518941</v>
       </c>
       <c r="B73">
-        <v>0.0010645825153812458</v>
+        <v>0.00082833801054708455</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.0050459753885794614</v>
       </c>
       <c r="B74">
-        <v>0.00093643082129802029</v>
+        <v>0.00070683894111765483</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.0044152284650070288</v>
       </c>
       <c r="B75">
-        <v>0.00080093454300914774</v>
+        <v>0.00057990659450451966</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.0037844815414345965</v>
       </c>
       <c r="B76">
-        <v>0.0006600965038587852</v>
+        <v>0.00045018392769387972</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.0031537346178621634</v>
       </c>
       <c r="B77">
-        <v>0.00051573593632246869</v>
+        <v>0.00032008293142591233</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.0025229876942897307</v>
       </c>
       <c r="B78">
-        <v>0.00036888344037761</v>
+        <v>0.00019101280793018413</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.0018922407707172983</v>
       </c>
       <c r="B79">
-        <v>0.00022148261002142181</v>
+        <v>6.5561970514316567E-05</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.0012614938471448654</v>
       </c>
       <c r="B80">
-        <v>7.7136888685239331E-05</v>
+        <v>-5.1535483723536867E-05</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.00063074692357243268</v>
       </c>
       <c r="B81">
-        <v>-5.4828755045602088E-05</v>
+        <v>-0.00014817929973432204</v>
       </c>
     </row>
     <row r="82" spans="1:2">
